--- a/Exp3_PTO_GRPO/eda/results/arms/validity/tables/gpt-4o-mini/validity.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/validity/tables/gpt-4o-mini/validity.xlsx
@@ -503,31 +503,31 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>54.8</v>
+        <v>54.5</v>
       </c>
       <c r="D2" t="n">
         <v>17.7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.407</v>
+        <v>0.409</v>
       </c>
       <c r="F2" t="n">
-        <v>0.411</v>
+        <v>0.413</v>
       </c>
       <c r="G2" t="n">
-        <v>0.412</v>
+        <v>0.413</v>
       </c>
       <c r="H2" t="n">
-        <v>0.418</v>
+        <v>0.419</v>
       </c>
       <c r="I2" t="n">
-        <v>0.386</v>
+        <v>0.387</v>
       </c>
       <c r="J2" t="n">
-        <v>0.402</v>
+        <v>0.396</v>
       </c>
       <c r="K2" t="n">
-        <v>0.033</v>
+        <v>0.029</v>
       </c>
       <c r="L2" t="n">
         <v>-0.025</v>
@@ -536,7 +536,7 @@
         <v>0.049</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.082</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="3">
@@ -549,37 +549,37 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>55</v>
+        <v>54.4</v>
       </c>
       <c r="D3" t="n">
         <v>17.8</v>
       </c>
       <c r="E3" t="n">
-        <v>0.401</v>
+        <v>0.405</v>
       </c>
       <c r="F3" t="n">
-        <v>0.411</v>
+        <v>0.413</v>
       </c>
       <c r="G3" t="n">
-        <v>0.412</v>
+        <v>0.413</v>
       </c>
       <c r="H3" t="n">
-        <v>0.417</v>
+        <v>0.418</v>
       </c>
       <c r="I3" t="n">
-        <v>0.382</v>
+        <v>0.385</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4</v>
+        <v>0.391</v>
       </c>
       <c r="K3" t="n">
-        <v>0.089</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.014</v>
+        <v>-0.015</v>
       </c>
       <c r="M3" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="N3" t="n">
         <v>-0.104</v>
@@ -595,40 +595,40 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>54.8</v>
+        <v>54.4</v>
       </c>
       <c r="D4" t="n">
         <v>20.1</v>
       </c>
       <c r="E4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.408</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.407</v>
       </c>
       <c r="H4" t="n">
         <v>0.417</v>
       </c>
       <c r="I4" t="n">
-        <v>0.388</v>
+        <v>0.389</v>
       </c>
       <c r="J4" t="n">
-        <v>0.405</v>
+        <v>0.4</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.044</v>
+        <v>-0.045</v>
       </c>
       <c r="L4" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
       <c r="M4" t="n">
         <v>0.093</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.011</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="5">
@@ -641,40 +641,40 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>55.7</v>
+        <v>55.2</v>
       </c>
       <c r="D5" t="n">
         <v>16.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.404</v>
+        <v>0.405</v>
       </c>
       <c r="F5" t="n">
-        <v>0.408</v>
+        <v>0.41</v>
       </c>
       <c r="G5" t="n">
-        <v>0.408</v>
+        <v>0.41</v>
       </c>
       <c r="H5" t="n">
-        <v>0.415</v>
+        <v>0.416</v>
       </c>
       <c r="I5" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="J5" t="n">
-        <v>0.397</v>
+        <v>0.39</v>
       </c>
       <c r="K5" t="n">
-        <v>0.049</v>
+        <v>0.044</v>
       </c>
       <c r="L5" t="n">
         <v>-0.08799999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.144</v>
+        <v>-0.142</v>
       </c>
     </row>
     <row r="6">
@@ -687,40 +687,40 @@
         <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>55.3</v>
+        <v>55.1</v>
       </c>
       <c r="D6" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="E6" t="n">
-        <v>0.409</v>
+        <v>0.41</v>
       </c>
       <c r="F6" t="n">
-        <v>0.409</v>
+        <v>0.41</v>
       </c>
       <c r="G6" t="n">
-        <v>0.411</v>
+        <v>0.412</v>
       </c>
       <c r="H6" t="n">
         <v>0.418</v>
       </c>
       <c r="I6" t="n">
-        <v>0.392</v>
+        <v>0.393</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4</v>
+        <v>0.397</v>
       </c>
       <c r="K6" t="n">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.033</v>
+        <v>-0.031</v>
       </c>
       <c r="M6" t="n">
         <v>0.06</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.053</v>
+        <v>-0.051</v>
       </c>
     </row>
     <row r="7">
